--- a/syama-ore-sorting/model/Syama_Pebble_Sorting_Simulation.xlsx
+++ b/syama-ore-sorting/model/Syama_Pebble_Sorting_Simulation.xlsx
@@ -24,9 +24,9 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="#,##0.000"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.000"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -133,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -144,33 +144,32 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -300,12 +299,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'NPV'!$D$12:$DS$12</f>
+              <f>'NPV'!$D$12:$EQ$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'NPV'!$D$14:$DS$14</f>
+              <f>'NPV'!$D$14:$EQ$14</f>
             </numRef>
           </val>
         </ser>
@@ -660,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -719,7 +718,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>STEINERT model SR241558 (Sukari) re-parameterised for Syama</t>
+          <t>African gold mine pebble sorting study (2024), re-parameterised for Syama</t>
         </is>
       </c>
     </row>
@@ -875,7 +874,7 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Assumption - CONFIRM</t>
+          <t>Syama - CONFIRM</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -909,7 +908,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>7884</v>
+        <v>7370</v>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
@@ -918,12 +917,12 @@
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>90% availability</t>
+          <t>African gold mine study, 2024</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>Assumption</t>
+          <t>Reference study</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -1166,7 +1165,7 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
@@ -1175,12 +1174,12 @@
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>8% base + Mali country-risk premium</t>
+          <t>African gold mine study, 2024</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Assumption</t>
+          <t>Reference study</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
@@ -1254,11 +1253,11 @@
     <row r="18">
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Milling cost avoided</t>
+          <t>Mining, dumping &amp; G&amp;A on rejects</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
@@ -1267,12 +1266,12 @@
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>power + media + reagents (Sukari used 7.69)</t>
+          <t>African gold mine study, 2024</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Assumption - CONFIRM</t>
+          <t>Reference study</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -1306,11 +1305,11 @@
     <row r="19">
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Incremental UG mining cost</t>
+          <t>Sorting OPEX</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>53</v>
+        <v>0.45</v>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
@@ -1319,12 +1318,12 @@
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>~45% of AISC $2,050/oz at 1.8 g/t recovered</t>
+          <t>African gold mine study, 2024</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Derived - CONFIRM</t>
+          <t>Reference study</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -1352,25 +1351,17 @@
       <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Reject rehandle + dump</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>$/t</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr"/>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>Assumption</t>
-        </is>
-      </c>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MATERIAL PROPERTY</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
       <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Au production</t>
@@ -1398,40 +1389,53 @@
     <row r="21">
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Sorting OPEX</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="n">
-        <v>0.45</v>
+          <t>Waste dilution</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>0.1190597374101857</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>$/t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>STEINERT template ($15/50 t/h + $0.15)</t>
+          <t>African gold mine study, 2024 - see note</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Vendor benchmark</t>
+          <t>Reference study</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  MATERIAL PROPERTY</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Undiluted ore grade</t>
+        </is>
+      </c>
+      <c r="C22" s="14">
+        <f>C12/(1-C21)</f>
+        <v/>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>g/t</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>ROM grade / (1 - dilution)</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  ECONOMICS   (sorting case less base case)</t>
@@ -1446,11 +1450,11 @@
     <row r="23">
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Waste dilution (SLC)</t>
+          <t>Circulating scat load</t>
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>0.2</v>
+        <v>0.16408</v>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
@@ -1459,12 +1463,12 @@
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>sublevel cave, typical 15-25%</t>
+          <t>of new feed; African gold mine study, 2024</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>Assumption - CONFIRM</t>
+          <t>Reference study</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -1472,7 +1476,7 @@
           <t>Incremental gold to leach</t>
         </is>
       </c>
-      <c r="K23" s="14">
+      <c r="K23" s="15">
         <f>L19</f>
         <v/>
       </c>
@@ -1485,26 +1489,25 @@
     <row r="24">
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Undiluted ore grade</t>
-        </is>
-      </c>
-      <c r="C24" s="15">
-        <f>C12/(1-C23)</f>
-        <v/>
+          <t>Mass yield ore -&gt; scats</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="n">
+        <v>0.1203</v>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>g/t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>ROM grade / (1 - dilution)</t>
+          <t>calibrated to the measured scat stream</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Calculated</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
@@ -1525,11 +1528,11 @@
     <row r="25">
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Mass yield ore -&gt; scats</t>
+          <t>Mass yield waste -&gt; scats</t>
         </is>
       </c>
       <c r="C25" s="16" t="n">
-        <v>0.1111</v>
+        <v>0.2682</v>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
@@ -1562,103 +1565,103 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Mass yield waste -&gt; scats</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="n">
-        <v>0.2</v>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>HETEROGENEITY CONTRAST</t>
+        </is>
+      </c>
+      <c r="C26" s="18">
+        <f>C25/C24</f>
+        <v/>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>waste yield / ore yield.   Reference study = 8.91x</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>KEY METRIC</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>Sorting OPEX</t>
+        </is>
+      </c>
+      <c r="K26" s="11">
+        <f>-C19*'MB Sort'!G106</f>
+        <v/>
+      </c>
+      <c r="M26" s="9" t="inlineStr">
+        <is>
+          <t>$/h</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SORTER PROPERTY</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Mining, dumping &amp; G&amp;A on rejects</t>
+        </is>
+      </c>
+      <c r="K27" s="11">
+        <f>-C18*'MB Sort'!G107</f>
+        <v/>
+      </c>
+      <c r="M27" s="9" t="inlineStr">
+        <is>
+          <t>$/h</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Sorter ore recovery</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>calibrated to the measured scat stream</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>Sorting OPEX</t>
-        </is>
-      </c>
-      <c r="K26" s="11">
-        <f>-C21*'MB Sort'!G106</f>
-        <v/>
-      </c>
-      <c r="M26" s="9" t="inlineStr">
-        <is>
-          <t>$/h</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>HETEROGENEITY CONTRAST</t>
-        </is>
-      </c>
-      <c r="C27" s="18">
-        <f>C26/C25</f>
-        <v/>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>waste yield / ore yield.   Sukari = 8.9x</t>
-        </is>
-      </c>
-      <c r="G27" s="10" t="inlineStr">
-        <is>
-          <t>KEY METRIC</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>Reject rehandle + dump</t>
-        </is>
-      </c>
-      <c r="K27" s="11">
-        <f>-C20*'MB Sort'!G107</f>
-        <v/>
-      </c>
-      <c r="M27" s="9" t="inlineStr">
-        <is>
-          <t>$/h</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  SORTER PROPERTY</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>Incremental mining cost</t>
-        </is>
-      </c>
-      <c r="K28" s="11">
-        <f>-C19*L9</f>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>African gold mine study, 2024</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Reference study</t>
+        </is>
+      </c>
+      <c r="I28" s="17" t="inlineStr">
+        <is>
+          <t>NET CASH BENEFIT</t>
+        </is>
+      </c>
+      <c r="K28" s="19">
+        <f>SUM(K25:K27)</f>
         <v/>
       </c>
       <c r="M28" s="9" t="inlineStr">
@@ -1670,11 +1673,11 @@
     <row r="29">
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Sorter ore recovery</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="n">
-        <v>0.95</v>
+          <t>Waste mass to rejects</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="n">
+        <v>0.9</v>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
@@ -1683,7 +1686,7 @@
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>XRT, conservatively tuned</t>
+          <t>African gold mine study, 2024</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
@@ -1691,279 +1694,256 @@
           <t>TEST WORK REQUIRED</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>Milling cost saved</t>
-        </is>
-      </c>
-      <c r="K29" s="11">
-        <f>-C18*L11</f>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>NET CASH BENEFIT</t>
+        </is>
+      </c>
+      <c r="K29" s="19">
+        <f>K28*C11</f>
         <v/>
       </c>
       <c r="M29" s="9" t="inlineStr">
         <is>
-          <t>$/h</t>
+          <t>$/a</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Waste mass to rejects</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CAPITAL &amp; EVALUATION</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="I30" s="17" t="inlineStr">
+        <is>
+          <t>NPV</t>
+        </is>
+      </c>
+      <c r="K30" s="19">
+        <f>NPV!B8</f>
+        <v/>
+      </c>
+      <c r="M30" s="9" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Sorting plant CAPEX</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>4095000</v>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>1 x 50 t/h sorter, reference build-up +30%</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>Reference study</t>
+        </is>
+      </c>
+      <c r="I31" s="17" t="inlineStr">
+        <is>
+          <t>IRR</t>
+        </is>
+      </c>
+      <c r="K31" s="21">
+        <f>NPV!B9</f>
+        <v/>
+      </c>
+      <c r="M31" s="9" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>XRT on Syama lithologies</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>TEST WORK REQUIRED</t>
-        </is>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
-        <is>
-          <t>NET CASH BENEFIT</t>
-        </is>
-      </c>
-      <c r="K30" s="20">
-        <f>SUM(K25:K29)</f>
-        <v/>
-      </c>
-      <c r="M30" s="9" t="inlineStr">
-        <is>
-          <t>$/h</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CAPITAL &amp; EVALUATION</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="I31" s="17" t="inlineStr">
-        <is>
-          <t>NET CASH BENEFIT</t>
-        </is>
-      </c>
-      <c r="K31" s="20">
-        <f>K30*C11</f>
-        <v/>
-      </c>
-      <c r="M31" s="9" t="inlineStr">
-        <is>
-          <t>$/a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Sorting plant CAPEX</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="n">
-        <v>4095000</v>
+          <t>Build period</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="n">
+        <v>12</v>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>months</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>1 x 50 t/h sorter, STEINERT build-up +30%</t>
+          <t>African gold mine study, 2024</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Vendor benchmark</t>
+          <t>Reference study</t>
         </is>
       </c>
       <c r="I32" s="17" t="inlineStr">
         <is>
-          <t>NPV</t>
-        </is>
-      </c>
-      <c r="K32" s="20">
-        <f>NPV!B8</f>
+          <t>Simple payback</t>
+        </is>
+      </c>
+      <c r="K32" s="23">
+        <f>IF(K29&gt;0,C31/K29*12,"n/a")</f>
         <v/>
       </c>
       <c r="M32" s="9" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>months</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Build period</t>
-        </is>
-      </c>
-      <c r="C33" s="21" t="n">
-        <v>12</v>
+          <t>Evaluation life</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="n">
+        <v>120</v>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
           <t>months</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>African gold mine study, 2024</t>
+        </is>
+      </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>Assumption</t>
-        </is>
-      </c>
-      <c r="I33" s="17" t="inlineStr">
-        <is>
-          <t>IRR</t>
-        </is>
-      </c>
-      <c r="K33" s="22">
-        <f>NPV!B9</f>
-        <v/>
-      </c>
-      <c r="M33" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>Reference study</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Evaluation life</t>
-        </is>
-      </c>
-      <c r="C34" s="21" t="n">
-        <v>96</v>
+          <t>ROM feed uplift  (Goal Seek)</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>8.640000000000001</v>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>t/h</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>8 years</t>
+          <t>Goal Seek: set L17 to 0 by changing this cell</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Assumption</t>
-        </is>
-      </c>
-      <c r="I34" s="17" t="inlineStr">
-        <is>
-          <t>Simple payback</t>
-        </is>
-      </c>
-      <c r="K34" s="23">
-        <f>IF(K31&gt;0,C32/K31*12,"n/a")</f>
-        <v/>
-      </c>
-      <c r="M34" s="9" t="inlineStr">
-        <is>
-          <t>months</t>
+          <t>Solved</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>ROM feed uplift  (Goal Seek)</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="n">
-        <v>7.2</v>
+          <t>Capacity capture factor</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>share of freed SAG capacity actually filled with ore</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>CRITICAL ASSUMPTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CALIBRATION CHECK  -  model must reproduce the measured scat stream</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Target circulating scat load</t>
+        </is>
+      </c>
+      <c r="C37" s="12">
+        <f>C23*C10</f>
+        <v/>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
           <t>t/h</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr">
-        <is>
-          <t>Goal Seek: set L17 to 0 by changing this cell</t>
-        </is>
-      </c>
-      <c r="G35" s="10" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Capacity capture factor</t>
-        </is>
-      </c>
-      <c r="C36" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>share of freed SAG capacity actually filled with ore</t>
-        </is>
-      </c>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>CRITICAL ASSUMPTION</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CALIBRATION CHECK  -  model must reproduce the measured scat stream</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>16.4% of new feed (African gold mine study, 2024)</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>Reference ratio</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Measured circulating scat load</t>
-        </is>
-      </c>
-      <c r="C38" s="24" t="n">
-        <v>30</v>
+          <t>MEASURED SCAT GRADE</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n">
+        <v>2</v>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>t/h</t>
+          <t>g/t</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>plant survey / client sampling</t>
+          <t>client sampling of SAG scats</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
@@ -1975,75 +1955,50 @@
     <row r="39">
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>MEASURED SCAT GRADE</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="n">
-        <v>2</v>
+          <t>Modelled circulating scat load</t>
+        </is>
+      </c>
+      <c r="C39" s="12">
+        <f>'MB Base'!G106</f>
+        <v/>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>g/t</t>
+          <t>t/h</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>plant survey / client sampling</t>
+          <t>adjust the two mass yields above until modelled = target</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>CLIENT DATA</t>
+          <t>calc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Modelled circulating scat load</t>
-        </is>
-      </c>
-      <c r="C40" s="25">
-        <f>'MB Base'!G106</f>
+          <t>Modelled scat grade</t>
+        </is>
+      </c>
+      <c r="C40" s="12">
+        <f>'MB Base'!H106</f>
         <v/>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>t/h</t>
+          <t>g/t</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>adjust the two mass yields above until modelled = measured</t>
+          <t>adjust the two mass yields above until modelled = target</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
-        <is>
-          <t>calc</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Modelled scat grade</t>
-        </is>
-      </c>
-      <c r="C41" s="12">
-        <f>'MB Base'!H106</f>
-        <v/>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>g/t</t>
-        </is>
-      </c>
-      <c r="F41" s="10" t="inlineStr">
-        <is>
-          <t>adjust the two mass yields above until modelled = measured</t>
-        </is>
-      </c>
-      <c r="G41" s="10" t="inlineStr">
         <is>
           <t>calc</t>
         </is>
@@ -2060,7 +2015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O118"/>
+  <dimension ref="B1:O119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2173,8 +2128,8 @@
           <t>Mass yield ore -&gt; oversize</t>
         </is>
       </c>
-      <c r="C3" s="26">
-        <f>Dashboard!C25</f>
+      <c r="C3" s="24">
+        <f>Dashboard!C24</f>
         <v/>
       </c>
       <c r="D3" s="9" t="inlineStr"/>
@@ -2185,8 +2140,8 @@
           <t>Mass yield waste -&gt; oversize</t>
         </is>
       </c>
-      <c r="C4" s="26">
-        <f>Dashboard!C26</f>
+      <c r="C4" s="24">
+        <f>Dashboard!C25</f>
         <v/>
       </c>
       <c r="D4" s="9" t="inlineStr"/>
@@ -2206,39 +2161,39 @@
           <t>PLANT FEED (new ROM)</t>
         </is>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="25">
         <f>K5+O5</f>
         <v/>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="25">
         <f>IFERROR(I5/G5,0)</f>
         <v/>
       </c>
-      <c r="I5" s="27">
+      <c r="I5" s="25">
         <f>M5</f>
         <v/>
       </c>
-      <c r="J5" s="28">
+      <c r="J5" s="26">
         <f>IFERROR(K5/G5,0)</f>
         <v/>
       </c>
-      <c r="K5" s="27">
+      <c r="K5" s="25">
         <f>Dashboard!C10*(1-$C$8)</f>
         <v/>
       </c>
-      <c r="L5" s="27">
-        <f>$C$7</f>
-        <v/>
-      </c>
-      <c r="M5" s="27">
+      <c r="L5" s="25">
+        <f>$C$7</f>
+        <v/>
+      </c>
+      <c r="M5" s="25">
         <f>K5*L5</f>
         <v/>
       </c>
-      <c r="N5" s="28">
+      <c r="N5" s="26">
         <f>IFERROR(O5/G5,0)</f>
         <v/>
       </c>
-      <c r="O5" s="27">
+      <c r="O5" s="25">
         <f>Dashboard!C10*$C$8</f>
         <v/>
       </c>
@@ -2260,8 +2215,8 @@
           <t>Undiluted ore grade</t>
         </is>
       </c>
-      <c r="C7" s="15">
-        <f>Dashboard!C24</f>
+      <c r="C7" s="14">
+        <f>Dashboard!C22</f>
         <v/>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -2277,26 +2232,26 @@
         </is>
       </c>
       <c r="C8" s="13">
-        <f>Dashboard!C23</f>
+        <f>Dashboard!C21</f>
         <v/>
       </c>
       <c r="D8" s="9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="F10" s="29" t="inlineStr">
+      <c r="F10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  RECIRCULATION PASS 1</t>
         </is>
       </c>
-      <c r="G10" s="29" t="n"/>
-      <c r="H10" s="29" t="n"/>
-      <c r="I10" s="29" t="n"/>
-      <c r="J10" s="29" t="n"/>
-      <c r="K10" s="29" t="n"/>
-      <c r="L10" s="29" t="n"/>
-      <c r="M10" s="29" t="n"/>
-      <c r="N10" s="29" t="n"/>
-      <c r="O10" s="29" t="n"/>
+      <c r="G10" s="27" t="n"/>
+      <c r="H10" s="27" t="n"/>
+      <c r="I10" s="27" t="n"/>
+      <c r="J10" s="27" t="n"/>
+      <c r="K10" s="27" t="n"/>
+      <c r="L10" s="27" t="n"/>
+      <c r="M10" s="27" t="n"/>
+      <c r="N10" s="27" t="n"/>
+      <c r="O10" s="27" t="n"/>
     </row>
     <row r="11">
       <c r="F11" s="9" t="inlineStr">
@@ -2385,7 +2340,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="F13" s="30" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>Mill discharge screen</t>
         </is>
@@ -2521,7 +2476,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="F17" s="30" t="inlineStr">
+      <c r="F17" s="28" t="inlineStr">
         <is>
           <t>Pebble sorter</t>
         </is>
@@ -2657,20 +2612,20 @@
       </c>
     </row>
     <row r="24">
-      <c r="F24" s="29" t="inlineStr">
+      <c r="F24" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  RECIRCULATION PASS 2</t>
         </is>
       </c>
-      <c r="G24" s="29" t="n"/>
-      <c r="H24" s="29" t="n"/>
-      <c r="I24" s="29" t="n"/>
-      <c r="J24" s="29" t="n"/>
-      <c r="K24" s="29" t="n"/>
-      <c r="L24" s="29" t="n"/>
-      <c r="M24" s="29" t="n"/>
-      <c r="N24" s="29" t="n"/>
-      <c r="O24" s="29" t="n"/>
+      <c r="G24" s="27" t="n"/>
+      <c r="H24" s="27" t="n"/>
+      <c r="I24" s="27" t="n"/>
+      <c r="J24" s="27" t="n"/>
+      <c r="K24" s="27" t="n"/>
+      <c r="L24" s="27" t="n"/>
+      <c r="M24" s="27" t="n"/>
+      <c r="N24" s="27" t="n"/>
+      <c r="O24" s="27" t="n"/>
     </row>
     <row r="25">
       <c r="F25" s="9" t="inlineStr">
@@ -2759,7 +2714,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="F27" s="30" t="inlineStr">
+      <c r="F27" s="28" t="inlineStr">
         <is>
           <t>Mill discharge screen</t>
         </is>
@@ -2895,7 +2850,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="F31" s="30" t="inlineStr">
+      <c r="F31" s="28" t="inlineStr">
         <is>
           <t>Pebble sorter</t>
         </is>
@@ -3031,20 +2986,20 @@
       </c>
     </row>
     <row r="38">
-      <c r="F38" s="29" t="inlineStr">
+      <c r="F38" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  RECIRCULATION PASS 3</t>
         </is>
       </c>
-      <c r="G38" s="29" t="n"/>
-      <c r="H38" s="29" t="n"/>
-      <c r="I38" s="29" t="n"/>
-      <c r="J38" s="29" t="n"/>
-      <c r="K38" s="29" t="n"/>
-      <c r="L38" s="29" t="n"/>
-      <c r="M38" s="29" t="n"/>
-      <c r="N38" s="29" t="n"/>
-      <c r="O38" s="29" t="n"/>
+      <c r="G38" s="27" t="n"/>
+      <c r="H38" s="27" t="n"/>
+      <c r="I38" s="27" t="n"/>
+      <c r="J38" s="27" t="n"/>
+      <c r="K38" s="27" t="n"/>
+      <c r="L38" s="27" t="n"/>
+      <c r="M38" s="27" t="n"/>
+      <c r="N38" s="27" t="n"/>
+      <c r="O38" s="27" t="n"/>
     </row>
     <row r="39">
       <c r="F39" s="9" t="inlineStr">
@@ -3133,7 +3088,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="F41" s="30" t="inlineStr">
+      <c r="F41" s="28" t="inlineStr">
         <is>
           <t>Mill discharge screen</t>
         </is>
@@ -3269,7 +3224,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="F45" s="30" t="inlineStr">
+      <c r="F45" s="28" t="inlineStr">
         <is>
           <t>Pebble sorter</t>
         </is>
@@ -3405,20 +3360,20 @@
       </c>
     </row>
     <row r="52">
-      <c r="F52" s="29" t="inlineStr">
+      <c r="F52" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  RECIRCULATION PASS 4</t>
         </is>
       </c>
-      <c r="G52" s="29" t="n"/>
-      <c r="H52" s="29" t="n"/>
-      <c r="I52" s="29" t="n"/>
-      <c r="J52" s="29" t="n"/>
-      <c r="K52" s="29" t="n"/>
-      <c r="L52" s="29" t="n"/>
-      <c r="M52" s="29" t="n"/>
-      <c r="N52" s="29" t="n"/>
-      <c r="O52" s="29" t="n"/>
+      <c r="G52" s="27" t="n"/>
+      <c r="H52" s="27" t="n"/>
+      <c r="I52" s="27" t="n"/>
+      <c r="J52" s="27" t="n"/>
+      <c r="K52" s="27" t="n"/>
+      <c r="L52" s="27" t="n"/>
+      <c r="M52" s="27" t="n"/>
+      <c r="N52" s="27" t="n"/>
+      <c r="O52" s="27" t="n"/>
     </row>
     <row r="53">
       <c r="F53" s="9" t="inlineStr">
@@ -3507,7 +3462,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="F55" s="30" t="inlineStr">
+      <c r="F55" s="28" t="inlineStr">
         <is>
           <t>Mill discharge screen</t>
         </is>
@@ -3643,7 +3598,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="F59" s="30" t="inlineStr">
+      <c r="F59" s="28" t="inlineStr">
         <is>
           <t>Pebble sorter</t>
         </is>
@@ -3779,20 +3734,20 @@
       </c>
     </row>
     <row r="66">
-      <c r="F66" s="29" t="inlineStr">
+      <c r="F66" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  RECIRCULATION PASS 5</t>
         </is>
       </c>
-      <c r="G66" s="29" t="n"/>
-      <c r="H66" s="29" t="n"/>
-      <c r="I66" s="29" t="n"/>
-      <c r="J66" s="29" t="n"/>
-      <c r="K66" s="29" t="n"/>
-      <c r="L66" s="29" t="n"/>
-      <c r="M66" s="29" t="n"/>
-      <c r="N66" s="29" t="n"/>
-      <c r="O66" s="29" t="n"/>
+      <c r="G66" s="27" t="n"/>
+      <c r="H66" s="27" t="n"/>
+      <c r="I66" s="27" t="n"/>
+      <c r="J66" s="27" t="n"/>
+      <c r="K66" s="27" t="n"/>
+      <c r="L66" s="27" t="n"/>
+      <c r="M66" s="27" t="n"/>
+      <c r="N66" s="27" t="n"/>
+      <c r="O66" s="27" t="n"/>
     </row>
     <row r="67">
       <c r="F67" s="9" t="inlineStr">
@@ -3881,7 +3836,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="F69" s="30" t="inlineStr">
+      <c r="F69" s="28" t="inlineStr">
         <is>
           <t>Mill discharge screen</t>
         </is>
@@ -4017,7 +3972,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="F73" s="30" t="inlineStr">
+      <c r="F73" s="28" t="inlineStr">
         <is>
           <t>Pebble sorter</t>
         </is>
@@ -4153,20 +4108,20 @@
       </c>
     </row>
     <row r="80">
-      <c r="F80" s="29" t="inlineStr">
+      <c r="F80" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  RECIRCULATION PASS 6</t>
         </is>
       </c>
-      <c r="G80" s="29" t="n"/>
-      <c r="H80" s="29" t="n"/>
-      <c r="I80" s="29" t="n"/>
-      <c r="J80" s="29" t="n"/>
-      <c r="K80" s="29" t="n"/>
-      <c r="L80" s="29" t="n"/>
-      <c r="M80" s="29" t="n"/>
-      <c r="N80" s="29" t="n"/>
-      <c r="O80" s="29" t="n"/>
+      <c r="G80" s="27" t="n"/>
+      <c r="H80" s="27" t="n"/>
+      <c r="I80" s="27" t="n"/>
+      <c r="J80" s="27" t="n"/>
+      <c r="K80" s="27" t="n"/>
+      <c r="L80" s="27" t="n"/>
+      <c r="M80" s="27" t="n"/>
+      <c r="N80" s="27" t="n"/>
+      <c r="O80" s="27" t="n"/>
     </row>
     <row r="81">
       <c r="F81" s="9" t="inlineStr">
@@ -4255,7 +4210,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="F83" s="30" t="inlineStr">
+      <c r="F83" s="28" t="inlineStr">
         <is>
           <t>Mill discharge screen</t>
         </is>
@@ -4391,7 +4346,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="F87" s="30" t="inlineStr">
+      <c r="F87" s="28" t="inlineStr">
         <is>
           <t>Pebble sorter</t>
         </is>
@@ -4629,7 +4584,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="F101" s="30" t="inlineStr">
+      <c r="F101" s="28" t="inlineStr">
         <is>
           <t>Mill discharge screen</t>
         </is>
@@ -4727,45 +4682,45 @@
           <t xml:space="preserve">   UNDERSIZE -&gt; ball mill / leach</t>
         </is>
       </c>
-      <c r="G104" s="31">
+      <c r="G104" s="29">
         <f>K104+O104</f>
         <v/>
       </c>
-      <c r="H104" s="31">
+      <c r="H104" s="29">
         <f>IFERROR(I104/G104,0)</f>
         <v/>
       </c>
-      <c r="I104" s="31">
+      <c r="I104" s="29">
         <f>M104</f>
         <v/>
       </c>
-      <c r="J104" s="32">
+      <c r="J104" s="30">
         <f>IFERROR(K104/G104,0)</f>
         <v/>
       </c>
-      <c r="K104" s="31">
+      <c r="K104" s="29">
         <f>K102-K103</f>
         <v/>
       </c>
-      <c r="L104" s="31">
-        <f>$C$7</f>
-        <v/>
-      </c>
-      <c r="M104" s="31">
+      <c r="L104" s="29">
+        <f>$C$7</f>
+        <v/>
+      </c>
+      <c r="M104" s="29">
         <f>K104*L104</f>
         <v/>
       </c>
-      <c r="N104" s="32">
+      <c r="N104" s="30">
         <f>IFERROR(O104/G104,0)</f>
         <v/>
       </c>
-      <c r="O104" s="31">
+      <c r="O104" s="29">
         <f>O102-O103</f>
         <v/>
       </c>
     </row>
     <row r="105">
-      <c r="F105" s="30" t="inlineStr">
+      <c r="F105" s="28" t="inlineStr">
         <is>
           <t>Pebble sorter</t>
         </is>
@@ -4777,39 +4732,39 @@
           <t xml:space="preserve">   SORTER FEED</t>
         </is>
       </c>
-      <c r="G106" s="33">
+      <c r="G106" s="31">
         <f>K106+O106</f>
         <v/>
       </c>
-      <c r="H106" s="33">
+      <c r="H106" s="31">
         <f>IFERROR(I106/G106,0)</f>
         <v/>
       </c>
-      <c r="I106" s="33">
+      <c r="I106" s="31">
         <f>M106</f>
         <v/>
       </c>
-      <c r="J106" s="19">
+      <c r="J106" s="20">
         <f>IFERROR(K106/G106,0)</f>
         <v/>
       </c>
-      <c r="K106" s="33">
+      <c r="K106" s="31">
         <f>K103</f>
         <v/>
       </c>
-      <c r="L106" s="33">
-        <f>$C$7</f>
-        <v/>
-      </c>
-      <c r="M106" s="33">
+      <c r="L106" s="31">
+        <f>$C$7</f>
+        <v/>
+      </c>
+      <c r="M106" s="31">
         <f>K106*L106</f>
         <v/>
       </c>
-      <c r="N106" s="19">
+      <c r="N106" s="20">
         <f>IFERROR(O106/G106,0)</f>
         <v/>
       </c>
-      <c r="O106" s="33">
+      <c r="O106" s="31">
         <f>O103</f>
         <v/>
       </c>
@@ -4820,39 +4775,39 @@
           <t xml:space="preserve">   REJECTS -&gt; waste dump</t>
         </is>
       </c>
-      <c r="G107" s="33">
+      <c r="G107" s="31">
         <f>K107+O107</f>
         <v/>
       </c>
-      <c r="H107" s="33">
+      <c r="H107" s="31">
         <f>IFERROR(I107/G107,0)</f>
         <v/>
       </c>
-      <c r="I107" s="33">
+      <c r="I107" s="31">
         <f>M107</f>
         <v/>
       </c>
-      <c r="J107" s="19">
+      <c r="J107" s="20">
         <f>IFERROR(K107/G107,0)</f>
         <v/>
       </c>
-      <c r="K107" s="33">
+      <c r="K107" s="31">
         <f>K106*(1-$C$5)</f>
         <v/>
       </c>
-      <c r="L107" s="33">
-        <f>$C$7</f>
-        <v/>
-      </c>
-      <c r="M107" s="33">
+      <c r="L107" s="31">
+        <f>$C$7</f>
+        <v/>
+      </c>
+      <c r="M107" s="31">
         <f>K107*L107</f>
         <v/>
       </c>
-      <c r="N107" s="19">
+      <c r="N107" s="20">
         <f>IFERROR(O107/G107,0)</f>
         <v/>
       </c>
-      <c r="O107" s="33">
+      <c r="O107" s="31">
         <f>O106*$C$6</f>
         <v/>
       </c>
@@ -4943,7 +4898,7 @@
           <t>Upgrade ratio (conc / feed)</t>
         </is>
       </c>
-      <c r="C114" s="15">
+      <c r="C114" s="14">
         <f>IFERROR(H108/H106,1)</f>
         <v/>
       </c>
@@ -4959,7 +4914,7 @@
           <t>Au lost to rejects</t>
         </is>
       </c>
-      <c r="C115" s="34">
+      <c r="C115" s="32">
         <f>I107</f>
         <v/>
       </c>
@@ -4991,7 +4946,7 @@
           <t>In-situ value of reject stream</t>
         </is>
       </c>
-      <c r="C117" s="34">
+      <c r="C117" s="32">
         <f>H107*Dashboard!C13*Dashboard!C15</f>
         <v/>
       </c>
@@ -5007,13 +4962,29 @@
           <t>Cost avoided per reject tonne</t>
         </is>
       </c>
-      <c r="C118" s="34">
-        <f>Dashboard!C18-Dashboard!C20</f>
+      <c r="C118" s="32">
+        <f>Dashboard!C18</f>
         <v/>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
           <t>$/t</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>Value discarded per $1 avoided</t>
+        </is>
+      </c>
+      <c r="C119" s="33">
+        <f>IFERROR(H107*Dashboard!C13*Dashboard!C15/Dashboard!C18,0)</f>
+        <v/>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
     </row>
@@ -5028,7 +4999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O118"/>
+  <dimension ref="B1:O119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -5141,8 +5112,8 @@
           <t>Mass yield ore -&gt; oversize</t>
         </is>
       </c>
-      <c r="C3" s="26">
-        <f>Dashboard!C25</f>
+      <c r="C3" s="24">
+        <f>Dashboard!C24</f>
         <v/>
       </c>
       <c r="D3" s="9" t="inlineStr"/>
@@ -5153,8 +5124,8 @@
           <t>Mass yield waste -&gt; oversize</t>
         </is>
       </c>
-      <c r="C4" s="26">
-        <f>Dashboard!C26</f>
+      <c r="C4" s="24">
+        <f>Dashboard!C25</f>
         <v/>
       </c>
       <c r="D4" s="9" t="inlineStr"/>
@@ -5166,7 +5137,7 @@
         </is>
       </c>
       <c r="C5" s="13">
-        <f>Dashboard!C29</f>
+        <f>Dashboard!C28</f>
         <v/>
       </c>
       <c r="D5" s="9" t="inlineStr"/>
@@ -5175,40 +5146,40 @@
           <t>PLANT FEED (new ROM)</t>
         </is>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="25">
         <f>K5+O5</f>
         <v/>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="25">
         <f>IFERROR(I5/G5,0)</f>
         <v/>
       </c>
-      <c r="I5" s="27">
+      <c r="I5" s="25">
         <f>M5</f>
         <v/>
       </c>
-      <c r="J5" s="28">
+      <c r="J5" s="26">
         <f>IFERROR(K5/G5,0)</f>
         <v/>
       </c>
-      <c r="K5" s="27">
-        <f>(Dashboard!C10+Dashboard!C35*Dashboard!C36)*(1-$C$8)</f>
-        <v/>
-      </c>
-      <c r="L5" s="27">
-        <f>$C$7</f>
-        <v/>
-      </c>
-      <c r="M5" s="27">
+      <c r="K5" s="25">
+        <f>(Dashboard!C10+Dashboard!C34*Dashboard!C35)*(1-$C$8)</f>
+        <v/>
+      </c>
+      <c r="L5" s="25">
+        <f>$C$7</f>
+        <v/>
+      </c>
+      <c r="M5" s="25">
         <f>K5*L5</f>
         <v/>
       </c>
-      <c r="N5" s="28">
+      <c r="N5" s="26">
         <f>IFERROR(O5/G5,0)</f>
         <v/>
       </c>
-      <c r="O5" s="27">
-        <f>(Dashboard!C10+Dashboard!C35*Dashboard!C36)*$C$8</f>
+      <c r="O5" s="25">
+        <f>(Dashboard!C10+Dashboard!C34*Dashboard!C35)*$C$8</f>
         <v/>
       </c>
     </row>
@@ -5219,7 +5190,7 @@
         </is>
       </c>
       <c r="C6" s="13">
-        <f>Dashboard!C30</f>
+        <f>Dashboard!C29</f>
         <v/>
       </c>
       <c r="D6" s="9" t="inlineStr"/>
@@ -5230,8 +5201,8 @@
           <t>Undiluted ore grade</t>
         </is>
       </c>
-      <c r="C7" s="15">
-        <f>Dashboard!C24</f>
+      <c r="C7" s="14">
+        <f>Dashboard!C22</f>
         <v/>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -5247,26 +5218,26 @@
         </is>
       </c>
       <c r="C8" s="13">
-        <f>Dashboard!C23</f>
+        <f>Dashboard!C21</f>
         <v/>
       </c>
       <c r="D8" s="9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="F10" s="29" t="inlineStr">
+      <c r="F10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  RECIRCULATION PASS 1</t>
         </is>
       </c>
-      <c r="G10" s="29" t="n"/>
-      <c r="H10" s="29" t="n"/>
-      <c r="I10" s="29" t="n"/>
-      <c r="J10" s="29" t="n"/>
-      <c r="K10" s="29" t="n"/>
-      <c r="L10" s="29" t="n"/>
-      <c r="M10" s="29" t="n"/>
-      <c r="N10" s="29" t="n"/>
-      <c r="O10" s="29" t="n"/>
+      <c r="G10" s="27" t="n"/>
+      <c r="H10" s="27" t="n"/>
+      <c r="I10" s="27" t="n"/>
+      <c r="J10" s="27" t="n"/>
+      <c r="K10" s="27" t="n"/>
+      <c r="L10" s="27" t="n"/>
+      <c r="M10" s="27" t="n"/>
+      <c r="N10" s="27" t="n"/>
+      <c r="O10" s="27" t="n"/>
     </row>
     <row r="11">
       <c r="F11" s="9" t="inlineStr">
@@ -5355,7 +5326,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="F13" s="30" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>Mill discharge screen</t>
         </is>
@@ -5491,7 +5462,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="F17" s="30" t="inlineStr">
+      <c r="F17" s="28" t="inlineStr">
         <is>
           <t>Pebble sorter</t>
         </is>
@@ -5627,20 +5598,20 @@
       </c>
     </row>
     <row r="24">
-      <c r="F24" s="29" t="inlineStr">
+      <c r="F24" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  RECIRCULATION PASS 2</t>
         </is>
       </c>
-      <c r="G24" s="29" t="n"/>
-      <c r="H24" s="29" t="n"/>
-      <c r="I24" s="29" t="n"/>
-      <c r="J24" s="29" t="n"/>
-      <c r="K24" s="29" t="n"/>
-      <c r="L24" s="29" t="n"/>
-      <c r="M24" s="29" t="n"/>
-      <c r="N24" s="29" t="n"/>
-      <c r="O24" s="29" t="n"/>
+      <c r="G24" s="27" t="n"/>
+      <c r="H24" s="27" t="n"/>
+      <c r="I24" s="27" t="n"/>
+      <c r="J24" s="27" t="n"/>
+      <c r="K24" s="27" t="n"/>
+      <c r="L24" s="27" t="n"/>
+      <c r="M24" s="27" t="n"/>
+      <c r="N24" s="27" t="n"/>
+      <c r="O24" s="27" t="n"/>
     </row>
     <row r="25">
       <c r="F25" s="9" t="inlineStr">
@@ -5729,7 +5700,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="F27" s="30" t="inlineStr">
+      <c r="F27" s="28" t="inlineStr">
         <is>
           <t>Mill discharge screen</t>
         </is>
@@ -5865,7 +5836,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="F31" s="30" t="inlineStr">
+      <c r="F31" s="28" t="inlineStr">
         <is>
           <t>Pebble sorter</t>
         </is>
@@ -6001,20 +5972,20 @@
       </c>
     </row>
     <row r="38">
-      <c r="F38" s="29" t="inlineStr">
+      <c r="F38" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  RECIRCULATION PASS 3</t>
         </is>
       </c>
-      <c r="G38" s="29" t="n"/>
-      <c r="H38" s="29" t="n"/>
-      <c r="I38" s="29" t="n"/>
-      <c r="J38" s="29" t="n"/>
-      <c r="K38" s="29" t="n"/>
-      <c r="L38" s="29" t="n"/>
-      <c r="M38" s="29" t="n"/>
-      <c r="N38" s="29" t="n"/>
-      <c r="O38" s="29" t="n"/>
+      <c r="G38" s="27" t="n"/>
+      <c r="H38" s="27" t="n"/>
+      <c r="I38" s="27" t="n"/>
+      <c r="J38" s="27" t="n"/>
+      <c r="K38" s="27" t="n"/>
+      <c r="L38" s="27" t="n"/>
+      <c r="M38" s="27" t="n"/>
+      <c r="N38" s="27" t="n"/>
+      <c r="O38" s="27" t="n"/>
     </row>
     <row r="39">
       <c r="F39" s="9" t="inlineStr">
@@ -6103,7 +6074,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="F41" s="30" t="inlineStr">
+      <c r="F41" s="28" t="inlineStr">
         <is>
           <t>Mill discharge screen</t>
         </is>
@@ -6239,7 +6210,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="F45" s="30" t="inlineStr">
+      <c r="F45" s="28" t="inlineStr">
         <is>
           <t>Pebble sorter</t>
         </is>
@@ -6375,20 +6346,20 @@
       </c>
     </row>
     <row r="52">
-      <c r="F52" s="29" t="inlineStr">
+      <c r="F52" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  RECIRCULATION PASS 4</t>
         </is>
       </c>
-      <c r="G52" s="29" t="n"/>
-      <c r="H52" s="29" t="n"/>
-      <c r="I52" s="29" t="n"/>
-      <c r="J52" s="29" t="n"/>
-      <c r="K52" s="29" t="n"/>
-      <c r="L52" s="29" t="n"/>
-      <c r="M52" s="29" t="n"/>
-      <c r="N52" s="29" t="n"/>
-      <c r="O52" s="29" t="n"/>
+      <c r="G52" s="27" t="n"/>
+      <c r="H52" s="27" t="n"/>
+      <c r="I52" s="27" t="n"/>
+      <c r="J52" s="27" t="n"/>
+      <c r="K52" s="27" t="n"/>
+      <c r="L52" s="27" t="n"/>
+      <c r="M52" s="27" t="n"/>
+      <c r="N52" s="27" t="n"/>
+      <c r="O52" s="27" t="n"/>
     </row>
     <row r="53">
       <c r="F53" s="9" t="inlineStr">
@@ -6477,7 +6448,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="F55" s="30" t="inlineStr">
+      <c r="F55" s="28" t="inlineStr">
         <is>
           <t>Mill discharge screen</t>
         </is>
@@ -6613,7 +6584,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="F59" s="30" t="inlineStr">
+      <c r="F59" s="28" t="inlineStr">
         <is>
           <t>Pebble sorter</t>
         </is>
@@ -6749,20 +6720,20 @@
       </c>
     </row>
     <row r="66">
-      <c r="F66" s="29" t="inlineStr">
+      <c r="F66" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  RECIRCULATION PASS 5</t>
         </is>
       </c>
-      <c r="G66" s="29" t="n"/>
-      <c r="H66" s="29" t="n"/>
-      <c r="I66" s="29" t="n"/>
-      <c r="J66" s="29" t="n"/>
-      <c r="K66" s="29" t="n"/>
-      <c r="L66" s="29" t="n"/>
-      <c r="M66" s="29" t="n"/>
-      <c r="N66" s="29" t="n"/>
-      <c r="O66" s="29" t="n"/>
+      <c r="G66" s="27" t="n"/>
+      <c r="H66" s="27" t="n"/>
+      <c r="I66" s="27" t="n"/>
+      <c r="J66" s="27" t="n"/>
+      <c r="K66" s="27" t="n"/>
+      <c r="L66" s="27" t="n"/>
+      <c r="M66" s="27" t="n"/>
+      <c r="N66" s="27" t="n"/>
+      <c r="O66" s="27" t="n"/>
     </row>
     <row r="67">
       <c r="F67" s="9" t="inlineStr">
@@ -6851,7 +6822,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="F69" s="30" t="inlineStr">
+      <c r="F69" s="28" t="inlineStr">
         <is>
           <t>Mill discharge screen</t>
         </is>
@@ -6987,7 +6958,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="F73" s="30" t="inlineStr">
+      <c r="F73" s="28" t="inlineStr">
         <is>
           <t>Pebble sorter</t>
         </is>
@@ -7123,20 +7094,20 @@
       </c>
     </row>
     <row r="80">
-      <c r="F80" s="29" t="inlineStr">
+      <c r="F80" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  RECIRCULATION PASS 6</t>
         </is>
       </c>
-      <c r="G80" s="29" t="n"/>
-      <c r="H80" s="29" t="n"/>
-      <c r="I80" s="29" t="n"/>
-      <c r="J80" s="29" t="n"/>
-      <c r="K80" s="29" t="n"/>
-      <c r="L80" s="29" t="n"/>
-      <c r="M80" s="29" t="n"/>
-      <c r="N80" s="29" t="n"/>
-      <c r="O80" s="29" t="n"/>
+      <c r="G80" s="27" t="n"/>
+      <c r="H80" s="27" t="n"/>
+      <c r="I80" s="27" t="n"/>
+      <c r="J80" s="27" t="n"/>
+      <c r="K80" s="27" t="n"/>
+      <c r="L80" s="27" t="n"/>
+      <c r="M80" s="27" t="n"/>
+      <c r="N80" s="27" t="n"/>
+      <c r="O80" s="27" t="n"/>
     </row>
     <row r="81">
       <c r="F81" s="9" t="inlineStr">
@@ -7225,7 +7196,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="F83" s="30" t="inlineStr">
+      <c r="F83" s="28" t="inlineStr">
         <is>
           <t>Mill discharge screen</t>
         </is>
@@ -7361,7 +7332,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="F87" s="30" t="inlineStr">
+      <c r="F87" s="28" t="inlineStr">
         <is>
           <t>Pebble sorter</t>
         </is>
@@ -7599,7 +7570,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="F101" s="30" t="inlineStr">
+      <c r="F101" s="28" t="inlineStr">
         <is>
           <t>Mill discharge screen</t>
         </is>
@@ -7697,45 +7668,45 @@
           <t xml:space="preserve">   UNDERSIZE -&gt; ball mill / leach</t>
         </is>
       </c>
-      <c r="G104" s="31">
+      <c r="G104" s="29">
         <f>K104+O104</f>
         <v/>
       </c>
-      <c r="H104" s="31">
+      <c r="H104" s="29">
         <f>IFERROR(I104/G104,0)</f>
         <v/>
       </c>
-      <c r="I104" s="31">
+      <c r="I104" s="29">
         <f>M104</f>
         <v/>
       </c>
-      <c r="J104" s="32">
+      <c r="J104" s="30">
         <f>IFERROR(K104/G104,0)</f>
         <v/>
       </c>
-      <c r="K104" s="31">
+      <c r="K104" s="29">
         <f>K102-K103</f>
         <v/>
       </c>
-      <c r="L104" s="31">
-        <f>$C$7</f>
-        <v/>
-      </c>
-      <c r="M104" s="31">
+      <c r="L104" s="29">
+        <f>$C$7</f>
+        <v/>
+      </c>
+      <c r="M104" s="29">
         <f>K104*L104</f>
         <v/>
       </c>
-      <c r="N104" s="32">
+      <c r="N104" s="30">
         <f>IFERROR(O104/G104,0)</f>
         <v/>
       </c>
-      <c r="O104" s="31">
+      <c r="O104" s="29">
         <f>O102-O103</f>
         <v/>
       </c>
     </row>
     <row r="105">
-      <c r="F105" s="30" t="inlineStr">
+      <c r="F105" s="28" t="inlineStr">
         <is>
           <t>Pebble sorter</t>
         </is>
@@ -7747,39 +7718,39 @@
           <t xml:space="preserve">   SORTER FEED</t>
         </is>
       </c>
-      <c r="G106" s="33">
+      <c r="G106" s="31">
         <f>K106+O106</f>
         <v/>
       </c>
-      <c r="H106" s="33">
+      <c r="H106" s="31">
         <f>IFERROR(I106/G106,0)</f>
         <v/>
       </c>
-      <c r="I106" s="33">
+      <c r="I106" s="31">
         <f>M106</f>
         <v/>
       </c>
-      <c r="J106" s="19">
+      <c r="J106" s="20">
         <f>IFERROR(K106/G106,0)</f>
         <v/>
       </c>
-      <c r="K106" s="33">
+      <c r="K106" s="31">
         <f>K103</f>
         <v/>
       </c>
-      <c r="L106" s="33">
-        <f>$C$7</f>
-        <v/>
-      </c>
-      <c r="M106" s="33">
+      <c r="L106" s="31">
+        <f>$C$7</f>
+        <v/>
+      </c>
+      <c r="M106" s="31">
         <f>K106*L106</f>
         <v/>
       </c>
-      <c r="N106" s="19">
+      <c r="N106" s="20">
         <f>IFERROR(O106/G106,0)</f>
         <v/>
       </c>
-      <c r="O106" s="33">
+      <c r="O106" s="31">
         <f>O103</f>
         <v/>
       </c>
@@ -7790,39 +7761,39 @@
           <t xml:space="preserve">   REJECTS -&gt; waste dump</t>
         </is>
       </c>
-      <c r="G107" s="33">
+      <c r="G107" s="31">
         <f>K107+O107</f>
         <v/>
       </c>
-      <c r="H107" s="33">
+      <c r="H107" s="31">
         <f>IFERROR(I107/G107,0)</f>
         <v/>
       </c>
-      <c r="I107" s="33">
+      <c r="I107" s="31">
         <f>M107</f>
         <v/>
       </c>
-      <c r="J107" s="19">
+      <c r="J107" s="20">
         <f>IFERROR(K107/G107,0)</f>
         <v/>
       </c>
-      <c r="K107" s="33">
+      <c r="K107" s="31">
         <f>K106*(1-$C$5)</f>
         <v/>
       </c>
-      <c r="L107" s="33">
-        <f>$C$7</f>
-        <v/>
-      </c>
-      <c r="M107" s="33">
+      <c r="L107" s="31">
+        <f>$C$7</f>
+        <v/>
+      </c>
+      <c r="M107" s="31">
         <f>K107*L107</f>
         <v/>
       </c>
-      <c r="N107" s="19">
+      <c r="N107" s="20">
         <f>IFERROR(O107/G107,0)</f>
         <v/>
       </c>
-      <c r="O107" s="33">
+      <c r="O107" s="31">
         <f>O106*$C$6</f>
         <v/>
       </c>
@@ -7913,7 +7884,7 @@
           <t>Upgrade ratio (conc / feed)</t>
         </is>
       </c>
-      <c r="C114" s="15">
+      <c r="C114" s="14">
         <f>IFERROR(H108/H106,1)</f>
         <v/>
       </c>
@@ -7929,7 +7900,7 @@
           <t>Au lost to rejects</t>
         </is>
       </c>
-      <c r="C115" s="34">
+      <c r="C115" s="32">
         <f>I107</f>
         <v/>
       </c>
@@ -7961,7 +7932,7 @@
           <t>In-situ value of reject stream</t>
         </is>
       </c>
-      <c r="C117" s="34">
+      <c r="C117" s="32">
         <f>H107*Dashboard!C13*Dashboard!C15</f>
         <v/>
       </c>
@@ -7977,13 +7948,29 @@
           <t>Cost avoided per reject tonne</t>
         </is>
       </c>
-      <c r="C118" s="34">
-        <f>Dashboard!C18-Dashboard!C20</f>
+      <c r="C118" s="32">
+        <f>Dashboard!C18</f>
         <v/>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
           <t>$/t</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>Value discarded per $1 avoided</t>
+        </is>
+      </c>
+      <c r="C119" s="33">
+        <f>IFERROR(H107*Dashboard!C13*Dashboard!C15/Dashboard!C18,0)</f>
+        <v/>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
     </row>
@@ -7998,7 +7985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DS14"/>
+  <dimension ref="A1:EQ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -8124,6 +8111,30 @@
     <col width="11" customWidth="1" min="121" max="121"/>
     <col width="11" customWidth="1" min="122" max="122"/>
     <col width="11" customWidth="1" min="123" max="123"/>
+    <col width="11" customWidth="1" min="124" max="124"/>
+    <col width="11" customWidth="1" min="125" max="125"/>
+    <col width="11" customWidth="1" min="126" max="126"/>
+    <col width="11" customWidth="1" min="127" max="127"/>
+    <col width="11" customWidth="1" min="128" max="128"/>
+    <col width="11" customWidth="1" min="129" max="129"/>
+    <col width="11" customWidth="1" min="130" max="130"/>
+    <col width="11" customWidth="1" min="131" max="131"/>
+    <col width="11" customWidth="1" min="132" max="132"/>
+    <col width="11" customWidth="1" min="133" max="133"/>
+    <col width="11" customWidth="1" min="134" max="134"/>
+    <col width="11" customWidth="1" min="135" max="135"/>
+    <col width="11" customWidth="1" min="136" max="136"/>
+    <col width="11" customWidth="1" min="137" max="137"/>
+    <col width="11" customWidth="1" min="138" max="138"/>
+    <col width="11" customWidth="1" min="139" max="139"/>
+    <col width="11" customWidth="1" min="140" max="140"/>
+    <col width="11" customWidth="1" min="141" max="141"/>
+    <col width="11" customWidth="1" min="142" max="142"/>
+    <col width="11" customWidth="1" min="143" max="143"/>
+    <col width="11" customWidth="1" min="144" max="144"/>
+    <col width="11" customWidth="1" min="145" max="145"/>
+    <col width="11" customWidth="1" min="146" max="146"/>
+    <col width="11" customWidth="1" min="147" max="147"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8147,7 +8158,7 @@
         </is>
       </c>
       <c r="B3" s="11">
-        <f>Dashboard!C32</f>
+        <f>Dashboard!C31</f>
         <v/>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -8163,7 +8174,7 @@
         </is>
       </c>
       <c r="B4" s="11">
-        <f>Dashboard!K31</f>
+        <f>Dashboard!K29</f>
         <v/>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -8190,8 +8201,8 @@
           <t>Build period</t>
         </is>
       </c>
-      <c r="B6" s="21">
-        <f>Dashboard!C33</f>
+      <c r="B6" s="22">
+        <f>Dashboard!C32</f>
         <v/>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -8206,8 +8217,8 @@
           <t>Evaluation life</t>
         </is>
       </c>
-      <c r="B7" s="21">
-        <f>Dashboard!C34</f>
+      <c r="B7" s="22">
+        <f>Dashboard!C33</f>
         <v/>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -8222,8 +8233,8 @@
           <t>NPV</t>
         </is>
       </c>
-      <c r="B8" s="20">
-        <f>NPV(B5/12,D13:DS13)</f>
+      <c r="B8" s="19">
+        <f>NPV(B5/12,D13:EQ13)</f>
         <v/>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -8238,8 +8249,8 @@
           <t>IRR (annualised)</t>
         </is>
       </c>
-      <c r="B9" s="22">
-        <f>IFERROR((1+IRR(D13:DS13))^12-1,"n/a")</f>
+      <c r="B9" s="21">
+        <f>IFERROR((1+IRR(D13:EQ13))^12-1,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -8265,365 +8276,437 @@
           <t>Month</t>
         </is>
       </c>
-      <c r="D12" s="35" t="n">
+      <c r="D12" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="35" t="n">
+      <c r="E12" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="35" t="n">
+      <c r="F12" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G12" s="35" t="n">
+      <c r="G12" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="35" t="n">
+      <c r="H12" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="35" t="n">
+      <c r="I12" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="J12" s="35" t="n">
+      <c r="J12" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="K12" s="35" t="n">
+      <c r="K12" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="L12" s="35" t="n">
+      <c r="L12" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="M12" s="35" t="n">
+      <c r="M12" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="N12" s="35" t="n">
+      <c r="N12" s="34" t="n">
         <v>11</v>
       </c>
-      <c r="O12" s="35" t="n">
+      <c r="O12" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="P12" s="35" t="n">
+      <c r="P12" s="34" t="n">
         <v>13</v>
       </c>
-      <c r="Q12" s="35" t="n">
+      <c r="Q12" s="34" t="n">
         <v>14</v>
       </c>
-      <c r="R12" s="35" t="n">
+      <c r="R12" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="S12" s="35" t="n">
+      <c r="S12" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="T12" s="35" t="n">
+      <c r="T12" s="34" t="n">
         <v>17</v>
       </c>
-      <c r="U12" s="35" t="n">
+      <c r="U12" s="34" t="n">
         <v>18</v>
       </c>
-      <c r="V12" s="35" t="n">
+      <c r="V12" s="34" t="n">
         <v>19</v>
       </c>
-      <c r="W12" s="35" t="n">
+      <c r="W12" s="34" t="n">
         <v>20</v>
       </c>
-      <c r="X12" s="35" t="n">
+      <c r="X12" s="34" t="n">
         <v>21</v>
       </c>
-      <c r="Y12" s="35" t="n">
+      <c r="Y12" s="34" t="n">
         <v>22</v>
       </c>
-      <c r="Z12" s="35" t="n">
+      <c r="Z12" s="34" t="n">
         <v>23</v>
       </c>
-      <c r="AA12" s="35" t="n">
+      <c r="AA12" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="AB12" s="35" t="n">
+      <c r="AB12" s="34" t="n">
         <v>25</v>
       </c>
-      <c r="AC12" s="35" t="n">
+      <c r="AC12" s="34" t="n">
         <v>26</v>
       </c>
-      <c r="AD12" s="35" t="n">
+      <c r="AD12" s="34" t="n">
         <v>27</v>
       </c>
-      <c r="AE12" s="35" t="n">
+      <c r="AE12" s="34" t="n">
         <v>28</v>
       </c>
-      <c r="AF12" s="35" t="n">
+      <c r="AF12" s="34" t="n">
         <v>29</v>
       </c>
-      <c r="AG12" s="35" t="n">
+      <c r="AG12" s="34" t="n">
         <v>30</v>
       </c>
-      <c r="AH12" s="35" t="n">
+      <c r="AH12" s="34" t="n">
         <v>31</v>
       </c>
-      <c r="AI12" s="35" t="n">
+      <c r="AI12" s="34" t="n">
         <v>32</v>
       </c>
-      <c r="AJ12" s="35" t="n">
+      <c r="AJ12" s="34" t="n">
         <v>33</v>
       </c>
-      <c r="AK12" s="35" t="n">
+      <c r="AK12" s="34" t="n">
         <v>34</v>
       </c>
-      <c r="AL12" s="35" t="n">
+      <c r="AL12" s="34" t="n">
         <v>35</v>
       </c>
-      <c r="AM12" s="35" t="n">
+      <c r="AM12" s="34" t="n">
         <v>36</v>
       </c>
-      <c r="AN12" s="35" t="n">
+      <c r="AN12" s="34" t="n">
         <v>37</v>
       </c>
-      <c r="AO12" s="35" t="n">
+      <c r="AO12" s="34" t="n">
         <v>38</v>
       </c>
-      <c r="AP12" s="35" t="n">
+      <c r="AP12" s="34" t="n">
         <v>39</v>
       </c>
-      <c r="AQ12" s="35" t="n">
+      <c r="AQ12" s="34" t="n">
         <v>40</v>
       </c>
-      <c r="AR12" s="35" t="n">
+      <c r="AR12" s="34" t="n">
         <v>41</v>
       </c>
-      <c r="AS12" s="35" t="n">
+      <c r="AS12" s="34" t="n">
         <v>42</v>
       </c>
-      <c r="AT12" s="35" t="n">
+      <c r="AT12" s="34" t="n">
         <v>43</v>
       </c>
-      <c r="AU12" s="35" t="n">
+      <c r="AU12" s="34" t="n">
         <v>44</v>
       </c>
-      <c r="AV12" s="35" t="n">
+      <c r="AV12" s="34" t="n">
         <v>45</v>
       </c>
-      <c r="AW12" s="35" t="n">
+      <c r="AW12" s="34" t="n">
         <v>46</v>
       </c>
-      <c r="AX12" s="35" t="n">
+      <c r="AX12" s="34" t="n">
         <v>47</v>
       </c>
-      <c r="AY12" s="35" t="n">
+      <c r="AY12" s="34" t="n">
         <v>48</v>
       </c>
-      <c r="AZ12" s="35" t="n">
+      <c r="AZ12" s="34" t="n">
         <v>49</v>
       </c>
-      <c r="BA12" s="35" t="n">
+      <c r="BA12" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="BB12" s="35" t="n">
+      <c r="BB12" s="34" t="n">
         <v>51</v>
       </c>
-      <c r="BC12" s="35" t="n">
+      <c r="BC12" s="34" t="n">
         <v>52</v>
       </c>
-      <c r="BD12" s="35" t="n">
+      <c r="BD12" s="34" t="n">
         <v>53</v>
       </c>
-      <c r="BE12" s="35" t="n">
+      <c r="BE12" s="34" t="n">
         <v>54</v>
       </c>
-      <c r="BF12" s="35" t="n">
+      <c r="BF12" s="34" t="n">
         <v>55</v>
       </c>
-      <c r="BG12" s="35" t="n">
+      <c r="BG12" s="34" t="n">
         <v>56</v>
       </c>
-      <c r="BH12" s="35" t="n">
+      <c r="BH12" s="34" t="n">
         <v>57</v>
       </c>
-      <c r="BI12" s="35" t="n">
+      <c r="BI12" s="34" t="n">
         <v>58</v>
       </c>
-      <c r="BJ12" s="35" t="n">
+      <c r="BJ12" s="34" t="n">
         <v>59</v>
       </c>
-      <c r="BK12" s="35" t="n">
+      <c r="BK12" s="34" t="n">
         <v>60</v>
       </c>
-      <c r="BL12" s="35" t="n">
+      <c r="BL12" s="34" t="n">
         <v>61</v>
       </c>
-      <c r="BM12" s="35" t="n">
+      <c r="BM12" s="34" t="n">
         <v>62</v>
       </c>
-      <c r="BN12" s="35" t="n">
+      <c r="BN12" s="34" t="n">
         <v>63</v>
       </c>
-      <c r="BO12" s="35" t="n">
+      <c r="BO12" s="34" t="n">
         <v>64</v>
       </c>
-      <c r="BP12" s="35" t="n">
+      <c r="BP12" s="34" t="n">
         <v>65</v>
       </c>
-      <c r="BQ12" s="35" t="n">
+      <c r="BQ12" s="34" t="n">
         <v>66</v>
       </c>
-      <c r="BR12" s="35" t="n">
+      <c r="BR12" s="34" t="n">
         <v>67</v>
       </c>
-      <c r="BS12" s="35" t="n">
+      <c r="BS12" s="34" t="n">
         <v>68</v>
       </c>
-      <c r="BT12" s="35" t="n">
+      <c r="BT12" s="34" t="n">
         <v>69</v>
       </c>
-      <c r="BU12" s="35" t="n">
+      <c r="BU12" s="34" t="n">
         <v>70</v>
       </c>
-      <c r="BV12" s="35" t="n">
+      <c r="BV12" s="34" t="n">
         <v>71</v>
       </c>
-      <c r="BW12" s="35" t="n">
+      <c r="BW12" s="34" t="n">
         <v>72</v>
       </c>
-      <c r="BX12" s="35" t="n">
+      <c r="BX12" s="34" t="n">
         <v>73</v>
       </c>
-      <c r="BY12" s="35" t="n">
+      <c r="BY12" s="34" t="n">
         <v>74</v>
       </c>
-      <c r="BZ12" s="35" t="n">
+      <c r="BZ12" s="34" t="n">
         <v>75</v>
       </c>
-      <c r="CA12" s="35" t="n">
+      <c r="CA12" s="34" t="n">
         <v>76</v>
       </c>
-      <c r="CB12" s="35" t="n">
+      <c r="CB12" s="34" t="n">
         <v>77</v>
       </c>
-      <c r="CC12" s="35" t="n">
+      <c r="CC12" s="34" t="n">
         <v>78</v>
       </c>
-      <c r="CD12" s="35" t="n">
+      <c r="CD12" s="34" t="n">
         <v>79</v>
       </c>
-      <c r="CE12" s="35" t="n">
+      <c r="CE12" s="34" t="n">
         <v>80</v>
       </c>
-      <c r="CF12" s="35" t="n">
+      <c r="CF12" s="34" t="n">
         <v>81</v>
       </c>
-      <c r="CG12" s="35" t="n">
+      <c r="CG12" s="34" t="n">
         <v>82</v>
       </c>
-      <c r="CH12" s="35" t="n">
+      <c r="CH12" s="34" t="n">
         <v>83</v>
       </c>
-      <c r="CI12" s="35" t="n">
+      <c r="CI12" s="34" t="n">
         <v>84</v>
       </c>
-      <c r="CJ12" s="35" t="n">
+      <c r="CJ12" s="34" t="n">
         <v>85</v>
       </c>
-      <c r="CK12" s="35" t="n">
+      <c r="CK12" s="34" t="n">
         <v>86</v>
       </c>
-      <c r="CL12" s="35" t="n">
+      <c r="CL12" s="34" t="n">
         <v>87</v>
       </c>
-      <c r="CM12" s="35" t="n">
+      <c r="CM12" s="34" t="n">
         <v>88</v>
       </c>
-      <c r="CN12" s="35" t="n">
+      <c r="CN12" s="34" t="n">
         <v>89</v>
       </c>
-      <c r="CO12" s="35" t="n">
+      <c r="CO12" s="34" t="n">
         <v>90</v>
       </c>
-      <c r="CP12" s="35" t="n">
+      <c r="CP12" s="34" t="n">
         <v>91</v>
       </c>
-      <c r="CQ12" s="35" t="n">
+      <c r="CQ12" s="34" t="n">
         <v>92</v>
       </c>
-      <c r="CR12" s="35" t="n">
+      <c r="CR12" s="34" t="n">
         <v>93</v>
       </c>
-      <c r="CS12" s="35" t="n">
+      <c r="CS12" s="34" t="n">
         <v>94</v>
       </c>
-      <c r="CT12" s="35" t="n">
+      <c r="CT12" s="34" t="n">
         <v>95</v>
       </c>
-      <c r="CU12" s="35" t="n">
+      <c r="CU12" s="34" t="n">
         <v>96</v>
       </c>
-      <c r="CV12" s="35" t="n">
+      <c r="CV12" s="34" t="n">
         <v>97</v>
       </c>
-      <c r="CW12" s="35" t="n">
+      <c r="CW12" s="34" t="n">
         <v>98</v>
       </c>
-      <c r="CX12" s="35" t="n">
+      <c r="CX12" s="34" t="n">
         <v>99</v>
       </c>
-      <c r="CY12" s="35" t="n">
+      <c r="CY12" s="34" t="n">
         <v>100</v>
       </c>
-      <c r="CZ12" s="35" t="n">
+      <c r="CZ12" s="34" t="n">
         <v>101</v>
       </c>
-      <c r="DA12" s="35" t="n">
+      <c r="DA12" s="34" t="n">
         <v>102</v>
       </c>
-      <c r="DB12" s="35" t="n">
+      <c r="DB12" s="34" t="n">
         <v>103</v>
       </c>
-      <c r="DC12" s="35" t="n">
+      <c r="DC12" s="34" t="n">
         <v>104</v>
       </c>
-      <c r="DD12" s="35" t="n">
+      <c r="DD12" s="34" t="n">
         <v>105</v>
       </c>
-      <c r="DE12" s="35" t="n">
+      <c r="DE12" s="34" t="n">
         <v>106</v>
       </c>
-      <c r="DF12" s="35" t="n">
+      <c r="DF12" s="34" t="n">
         <v>107</v>
       </c>
-      <c r="DG12" s="35" t="n">
+      <c r="DG12" s="34" t="n">
         <v>108</v>
       </c>
-      <c r="DH12" s="35" t="n">
+      <c r="DH12" s="34" t="n">
         <v>109</v>
       </c>
-      <c r="DI12" s="35" t="n">
+      <c r="DI12" s="34" t="n">
         <v>110</v>
       </c>
-      <c r="DJ12" s="35" t="n">
+      <c r="DJ12" s="34" t="n">
         <v>111</v>
       </c>
-      <c r="DK12" s="35" t="n">
+      <c r="DK12" s="34" t="n">
         <v>112</v>
       </c>
-      <c r="DL12" s="35" t="n">
+      <c r="DL12" s="34" t="n">
         <v>113</v>
       </c>
-      <c r="DM12" s="35" t="n">
+      <c r="DM12" s="34" t="n">
         <v>114</v>
       </c>
-      <c r="DN12" s="35" t="n">
+      <c r="DN12" s="34" t="n">
         <v>115</v>
       </c>
-      <c r="DO12" s="35" t="n">
+      <c r="DO12" s="34" t="n">
         <v>116</v>
       </c>
-      <c r="DP12" s="35" t="n">
+      <c r="DP12" s="34" t="n">
         <v>117</v>
       </c>
-      <c r="DQ12" s="35" t="n">
+      <c r="DQ12" s="34" t="n">
         <v>118</v>
       </c>
-      <c r="DR12" s="35" t="n">
+      <c r="DR12" s="34" t="n">
         <v>119</v>
       </c>
-      <c r="DS12" s="35" t="n">
+      <c r="DS12" s="34" t="n">
         <v>120</v>
+      </c>
+      <c r="DT12" s="34" t="n">
+        <v>121</v>
+      </c>
+      <c r="DU12" s="34" t="n">
+        <v>122</v>
+      </c>
+      <c r="DV12" s="34" t="n">
+        <v>123</v>
+      </c>
+      <c r="DW12" s="34" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX12" s="34" t="n">
+        <v>125</v>
+      </c>
+      <c r="DY12" s="34" t="n">
+        <v>126</v>
+      </c>
+      <c r="DZ12" s="34" t="n">
+        <v>127</v>
+      </c>
+      <c r="EA12" s="34" t="n">
+        <v>128</v>
+      </c>
+      <c r="EB12" s="34" t="n">
+        <v>129</v>
+      </c>
+      <c r="EC12" s="34" t="n">
+        <v>130</v>
+      </c>
+      <c r="ED12" s="34" t="n">
+        <v>131</v>
+      </c>
+      <c r="EE12" s="34" t="n">
+        <v>132</v>
+      </c>
+      <c r="EF12" s="34" t="n">
+        <v>133</v>
+      </c>
+      <c r="EG12" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="EH12" s="34" t="n">
+        <v>135</v>
+      </c>
+      <c r="EI12" s="34" t="n">
+        <v>136</v>
+      </c>
+      <c r="EJ12" s="34" t="n">
+        <v>137</v>
+      </c>
+      <c r="EK12" s="34" t="n">
+        <v>138</v>
+      </c>
+      <c r="EL12" s="34" t="n">
+        <v>139</v>
+      </c>
+      <c r="EM12" s="34" t="n">
+        <v>140</v>
+      </c>
+      <c r="EN12" s="34" t="n">
+        <v>141</v>
+      </c>
+      <c r="EO12" s="34" t="n">
+        <v>142</v>
+      </c>
+      <c r="EP12" s="34" t="n">
+        <v>143</v>
+      </c>
+      <c r="EQ12" s="34" t="n">
+        <v>144</v>
       </c>
     </row>
     <row r="13">
@@ -9112,6 +9195,102 @@
         <f>IF(DS$12=1,-$B$3,0)+IF(AND(DS$12&gt;$B$6,DS$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
         <v/>
       </c>
+      <c r="DT13" s="11">
+        <f>IF(DT$12=1,-$B$3,0)+IF(AND(DT$12&gt;$B$6,DT$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="DU13" s="11">
+        <f>IF(DU$12=1,-$B$3,0)+IF(AND(DU$12&gt;$B$6,DU$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="DV13" s="11">
+        <f>IF(DV$12=1,-$B$3,0)+IF(AND(DV$12&gt;$B$6,DV$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="DW13" s="11">
+        <f>IF(DW$12=1,-$B$3,0)+IF(AND(DW$12&gt;$B$6,DW$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="DX13" s="11">
+        <f>IF(DX$12=1,-$B$3,0)+IF(AND(DX$12&gt;$B$6,DX$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="DY13" s="11">
+        <f>IF(DY$12=1,-$B$3,0)+IF(AND(DY$12&gt;$B$6,DY$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="DZ13" s="11">
+        <f>IF(DZ$12=1,-$B$3,0)+IF(AND(DZ$12&gt;$B$6,DZ$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="EA13" s="11">
+        <f>IF(EA$12=1,-$B$3,0)+IF(AND(EA$12&gt;$B$6,EA$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="EB13" s="11">
+        <f>IF(EB$12=1,-$B$3,0)+IF(AND(EB$12&gt;$B$6,EB$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="EC13" s="11">
+        <f>IF(EC$12=1,-$B$3,0)+IF(AND(EC$12&gt;$B$6,EC$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="ED13" s="11">
+        <f>IF(ED$12=1,-$B$3,0)+IF(AND(ED$12&gt;$B$6,ED$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="EE13" s="11">
+        <f>IF(EE$12=1,-$B$3,0)+IF(AND(EE$12&gt;$B$6,EE$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="EF13" s="11">
+        <f>IF(EF$12=1,-$B$3,0)+IF(AND(EF$12&gt;$B$6,EF$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="EG13" s="11">
+        <f>IF(EG$12=1,-$B$3,0)+IF(AND(EG$12&gt;$B$6,EG$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="EH13" s="11">
+        <f>IF(EH$12=1,-$B$3,0)+IF(AND(EH$12&gt;$B$6,EH$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="EI13" s="11">
+        <f>IF(EI$12=1,-$B$3,0)+IF(AND(EI$12&gt;$B$6,EI$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="EJ13" s="11">
+        <f>IF(EJ$12=1,-$B$3,0)+IF(AND(EJ$12&gt;$B$6,EJ$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="EK13" s="11">
+        <f>IF(EK$12=1,-$B$3,0)+IF(AND(EK$12&gt;$B$6,EK$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="EL13" s="11">
+        <f>IF(EL$12=1,-$B$3,0)+IF(AND(EL$12&gt;$B$6,EL$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="EM13" s="11">
+        <f>IF(EM$12=1,-$B$3,0)+IF(AND(EM$12&gt;$B$6,EM$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="EN13" s="11">
+        <f>IF(EN$12=1,-$B$3,0)+IF(AND(EN$12&gt;$B$6,EN$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="EO13" s="11">
+        <f>IF(EO$12=1,-$B$3,0)+IF(AND(EO$12&gt;$B$6,EO$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="EP13" s="11">
+        <f>IF(EP$12=1,-$B$3,0)+IF(AND(EP$12&gt;$B$6,EP$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
+      <c r="EQ13" s="11">
+        <f>IF(EQ$12=1,-$B$3,0)+IF(AND(EQ$12&gt;$B$6,EQ$12&lt;=$B$6+$B$7),$B$4/12,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -9597,6 +9776,102 @@
       </c>
       <c r="DS14" s="11">
         <f>DR14+DS13</f>
+        <v/>
+      </c>
+      <c r="DT14" s="11">
+        <f>DS14+DT13</f>
+        <v/>
+      </c>
+      <c r="DU14" s="11">
+        <f>DT14+DU13</f>
+        <v/>
+      </c>
+      <c r="DV14" s="11">
+        <f>DU14+DV13</f>
+        <v/>
+      </c>
+      <c r="DW14" s="11">
+        <f>DV14+DW13</f>
+        <v/>
+      </c>
+      <c r="DX14" s="11">
+        <f>DW14+DX13</f>
+        <v/>
+      </c>
+      <c r="DY14" s="11">
+        <f>DX14+DY13</f>
+        <v/>
+      </c>
+      <c r="DZ14" s="11">
+        <f>DY14+DZ13</f>
+        <v/>
+      </c>
+      <c r="EA14" s="11">
+        <f>DZ14+EA13</f>
+        <v/>
+      </c>
+      <c r="EB14" s="11">
+        <f>EA14+EB13</f>
+        <v/>
+      </c>
+      <c r="EC14" s="11">
+        <f>EB14+EC13</f>
+        <v/>
+      </c>
+      <c r="ED14" s="11">
+        <f>EC14+ED13</f>
+        <v/>
+      </c>
+      <c r="EE14" s="11">
+        <f>ED14+EE13</f>
+        <v/>
+      </c>
+      <c r="EF14" s="11">
+        <f>EE14+EF13</f>
+        <v/>
+      </c>
+      <c r="EG14" s="11">
+        <f>EF14+EG13</f>
+        <v/>
+      </c>
+      <c r="EH14" s="11">
+        <f>EG14+EH13</f>
+        <v/>
+      </c>
+      <c r="EI14" s="11">
+        <f>EH14+EI13</f>
+        <v/>
+      </c>
+      <c r="EJ14" s="11">
+        <f>EI14+EJ13</f>
+        <v/>
+      </c>
+      <c r="EK14" s="11">
+        <f>EJ14+EK13</f>
+        <v/>
+      </c>
+      <c r="EL14" s="11">
+        <f>EK14+EL13</f>
+        <v/>
+      </c>
+      <c r="EM14" s="11">
+        <f>EL14+EM13</f>
+        <v/>
+      </c>
+      <c r="EN14" s="11">
+        <f>EM14+EN13</f>
+        <v/>
+      </c>
+      <c r="EO14" s="11">
+        <f>EN14+EO13</f>
+        <v/>
+      </c>
+      <c r="EP14" s="11">
+        <f>EO14+EP13</f>
+        <v/>
+      </c>
+      <c r="EQ14" s="11">
+        <f>EP14+EQ13</f>
         <v/>
       </c>
     </row>
@@ -9638,9 +9913,9 @@
       <c r="G1" s="1" t="n"/>
     </row>
     <row r="3">
-      <c r="B3" s="36" t="inlineStr">
-        <is>
-          <t>Values are static (generated with the model engine). Re-run build_wb.py to refresh after changing Dashboard inputs.</t>
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>Values are static (generated by sensitivity.py). Re-run it, then build_workbook.py, to refresh after changing Dashboard inputs.</t>
         </is>
       </c>
     </row>
@@ -9683,136 +9958,136 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="14" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>-566.7792973709322</v>
+        <v>-1150.633744558641</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>-1964634.979889435</v>
-      </c>
-      <c r="F7" s="38" t="n">
-        <v>-13861666.51034132</v>
+        <v>-5172491.237029027</v>
+      </c>
+      <c r="F7" s="37" t="n">
+        <v>-36899292.2291428</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="C8" s="15" t="n">
-        <v>0.7201533406352667</v>
+      <c r="C8" s="14" t="n">
+        <v>0.8639603735617926</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>-240.2448938472752</v>
+        <v>-787.1152317179743</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>-1010560.449842954</v>
-      </c>
-      <c r="F8" s="38" t="n">
-        <v>-9118735.708254609</v>
+        <v>-3720879.283777669</v>
+      </c>
+      <c r="F8" s="37" t="n">
+        <v>-27693070.21046118</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="37" t="inlineStr">
-        <is>
-          <t>21%</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="n">
-        <v>1.51232201533406</v>
+      <c r="B9" s="36" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>2.159900933904481</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>118.942950028782</v>
+        <v>-241.8374624568929</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>38921.53320830893</v>
-      </c>
-      <c r="F9" s="38" t="n">
-        <v>-3901511.825958568</v>
+        <v>-1543461.353900308</v>
+      </c>
+      <c r="F9" s="37" t="n">
+        <v>-13883737.18243671</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="37" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="n">
-        <v>1.800383351588167</v>
+      <c r="B10" s="36" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>3.45584149424717</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>249.5567114382534</v>
+        <v>303.4403068041482</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>420551.345226933</v>
-      </c>
-      <c r="F10" s="38" t="n">
-        <v>-2004339.505123731</v>
+        <v>633956.5759768917</v>
+      </c>
+      <c r="F10" s="37" t="n">
+        <v>-74404.15441325886</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="37" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="C11" s="15" t="n">
-        <v>3.600766703176333</v>
+      <c r="C11" s="14" t="n">
+        <v>4.319801867808962</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>1065.892720247396</v>
+        <v>666.9588196448051</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>2805737.67034314</v>
-      </c>
-      <c r="F11" s="39" t="n">
-        <v>9852987.50009306</v>
+        <v>2085568.52922821</v>
+      </c>
+      <c r="F11" s="38" t="n">
+        <v>9131817.864268105</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="C12" s="15" t="n">
-        <v>5.4011500547645</v>
+      <c r="C12" s="14" t="n">
+        <v>6.479702801713444</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1882.228729056549</v>
+        <v>1575.755101746553</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>5190923.995459381</v>
-      </c>
-      <c r="F12" s="39" t="n">
-        <v>21710314.50531001</v>
+        <v>5714598.412356929</v>
+      </c>
+      <c r="F12" s="38" t="n">
+        <v>32147372.91097418</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="C13" s="15" t="n">
-        <v>7.201533406352667</v>
+      <c r="C13" s="14" t="n">
+        <v>8.639603735617925</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>2698.564737865702</v>
+        <v>2484.551383848262</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>7576110.32057563</v>
-      </c>
-      <c r="F13" s="39" t="n">
-        <v>33567641.51052701</v>
+        <v>9343628.295485487</v>
+      </c>
+      <c r="F13" s="38" t="n">
+        <v>55162927.95767928</v>
       </c>
     </row>
     <row r="16">
@@ -9854,105 +10129,105 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="40" t="n">
+      <c r="B18" s="39" t="n">
         <v>0.8</v>
       </c>
-      <c r="C18" s="15" t="n">
-        <v>7.201533406352667</v>
+      <c r="C18" s="14" t="n">
+        <v>8.639603735617925</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>521.6687143746269</v>
+        <v>61.09463157700307</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>-1131473.773388669</v>
-      </c>
-      <c r="F18" s="38" t="n">
-        <v>-9719824.521095792</v>
+        <v>-350198.7135995468</v>
+      </c>
+      <c r="F18" s="37" t="n">
+        <v>-6315984.127908916</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="40" t="n">
+      <c r="B19" s="39" t="n">
         <v>1.2</v>
       </c>
-      <c r="C19" s="15" t="n">
-        <v>7.201533406352667</v>
+      <c r="C19" s="14" t="n">
+        <v>8.639603735617925</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1065.892720247396</v>
+        <v>666.9588196448051</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1045422.250102406</v>
-      </c>
-      <c r="F19" s="39" t="n">
-        <v>1102041.986809907</v>
+        <v>2073258.038671661</v>
+      </c>
+      <c r="F19" s="38" t="n">
+        <v>9053743.893487804</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="40" t="n">
+      <c r="B20" s="39" t="n">
         <v>1.6</v>
       </c>
-      <c r="C20" s="15" t="n">
-        <v>7.201533406352667</v>
+      <c r="C20" s="14" t="n">
+        <v>8.639603735617925</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1610.116726120175</v>
+        <v>1272.823007712617</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>3222318.273593523</v>
-      </c>
-      <c r="F20" s="39" t="n">
-        <v>11923908.49471581</v>
+        <v>4496714.790942909</v>
+      </c>
+      <c r="F20" s="38" t="n">
+        <v>24423471.91488479</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="40" t="n">
+      <c r="B21" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="C21" s="15" t="n">
-        <v>7.201533406352667</v>
+      <c r="C21" s="14" t="n">
+        <v>8.639603735617925</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>2154.340731992944</v>
+        <v>1878.687195780439</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>5399214.2970846</v>
-      </c>
-      <c r="F21" s="39" t="n">
-        <v>22745775.00262152</v>
+        <v>6920171.543214198</v>
+      </c>
+      <c r="F21" s="38" t="n">
+        <v>39793199.93628203</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="40" t="n">
+      <c r="B22" s="39" t="n">
         <v>2.4</v>
       </c>
-      <c r="C22" s="15" t="n">
-        <v>7.201533406352667</v>
+      <c r="C22" s="14" t="n">
+        <v>8.639603735617925</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>2698.564737865702</v>
+        <v>2484.551383848262</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>7576110.32057563</v>
-      </c>
-      <c r="F22" s="39" t="n">
-        <v>33567641.51052701</v>
+        <v>9343628.295485487</v>
+      </c>
+      <c r="F22" s="38" t="n">
+        <v>55162927.95767928</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="40" t="n">
+      <c r="B23" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="C23" s="15" t="n">
-        <v>7.201533406352667</v>
+      <c r="C23" s="14" t="n">
+        <v>8.639603735617925</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>3514.900746674844</v>
+        <v>3393.34766594999</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>10841454.3558122</v>
-      </c>
-      <c r="F23" s="39" t="n">
-        <v>49800441.27238534</v>
+        <v>12978813.4238924</v>
+      </c>
+      <c r="F23" s="38" t="n">
+        <v>78217519.98977496</v>
       </c>
     </row>
     <row r="26">
@@ -10000,123 +10275,123 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="40" t="n">
+      <c r="B28" s="39" t="n">
         <v>0.5</v>
       </c>
-      <c r="C28" s="15" t="n">
-        <v>12.69230769263757</v>
-      </c>
-      <c r="D28" s="15" t="n">
-        <v>0.06027516924919286</v>
+      <c r="C28" s="14" t="n">
+        <v>16.01820481480498</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>0.1299722837015145</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>0.5550303030336123</v>
+        <v>0.6513906429626953</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>18073950.13557444</v>
-      </c>
-      <c r="G28" s="39" t="n">
-        <v>85754893.39272992</v>
+        <v>20835314.27571358</v>
+      </c>
+      <c r="G28" s="38" t="n">
+        <v>128043984.2661426</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="40" t="n">
+      <c r="B29" s="39" t="n">
         <v>0.8</v>
       </c>
-      <c r="C29" s="15" t="n">
-        <v>7.451612903252887</v>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>0.1039237142406425</v>
+      <c r="C29" s="14" t="n">
+        <v>9.512153274411034</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>0.2161763798033032</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>0.4826467481520899</v>
+        <v>0.5505277680645975</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>16196929.97013785</v>
-      </c>
-      <c r="G29" s="39" t="n">
-        <v>76423780.90788727</v>
+        <v>19148873.20833964</v>
+      </c>
+      <c r="G29" s="38" t="n">
+        <v>117348459.9885338</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="40" t="n">
+      <c r="B30" s="39" t="n">
         <v>1.2</v>
       </c>
-      <c r="C30" s="15" t="n">
-        <v>4.44827586206957</v>
-      </c>
-      <c r="D30" s="15" t="n">
-        <v>0.1761652246720378</v>
+      <c r="C30" s="14" t="n">
+        <v>5.74231677754614</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>0.3490832451785792</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>0.3969643252825414</v>
+        <v>0.4444287261721391</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>13536549.66217588</v>
-      </c>
-      <c r="G30" s="39" t="n">
-        <v>63198399.3359853</v>
+        <v>16518878.07180036</v>
+      </c>
+      <c r="G30" s="38" t="n">
+        <v>100668851.4465939</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="40" t="n">
+      <c r="B31" s="39" t="n">
         <v>1.6</v>
       </c>
-      <c r="C31" s="15" t="n">
-        <v>2.851851851851855</v>
-      </c>
-      <c r="D31" s="15" t="n">
-        <v>0.27551867219917</v>
+      <c r="C31" s="14" t="n">
+        <v>3.676994603916482</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>0.5210137347339557</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>0.3190644307149164</v>
+        <v>0.3557396729234555</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>10672874.07546342</v>
-      </c>
-      <c r="G31" s="39" t="n">
-        <v>48962388.71033689</v>
+        <v>13320844.46461406</v>
+      </c>
+      <c r="G31" s="38" t="n">
+        <v>80386704.17919387</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="40" t="n">
+      <c r="B32" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="15" t="n">
-        <v>1.799999999999999</v>
-      </c>
-      <c r="D32" s="15" t="n">
-        <v>0.4288973384030423</v>
+      <c r="C32" s="14" t="n">
+        <v>2.22936330185598</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>0.7817907848321594</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>0.2448789571694599</v>
+        <v>0.273082837814269</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>7576110.32057563</v>
-      </c>
-      <c r="G32" s="39" t="n">
-        <v>33567641.51052701</v>
+        <v>9343628.295485487</v>
+      </c>
+      <c r="G32" s="38" t="n">
+        <v>55162927.95767928</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="40" t="n">
+      <c r="B33" s="39" t="n">
         <v>2.4</v>
       </c>
-      <c r="C33" s="15" t="n">
-        <v>0.9999999999999991</v>
-      </c>
-      <c r="D33" s="15" t="n">
-        <v>0.7157894736842113</v>
+      <c r="C33" s="14" t="n">
+        <v>0.9999999999999992</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>1.311531524936556</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>0.1706586826347305</v>
+        <v>0.1855184406924918</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>4210344.997129409</v>
-      </c>
-      <c r="G33" s="39" t="n">
-        <v>16835623.70433877</v>
+        <v>4256639.487152244</v>
+      </c>
+      <c r="G33" s="38" t="n">
+        <v>22900897.96325201</v>
       </c>
     </row>
     <row r="36">
@@ -10164,97 +10439,97 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="37" t="inlineStr">
+      <c r="B38" s="36" t="inlineStr">
         <is>
           <t>99% / 50%</t>
         </is>
       </c>
       <c r="C38" s="13" t="n">
-        <v>0.1608996539792387</v>
-      </c>
-      <c r="D38" s="15" t="n">
-        <v>0.1290322580645163</v>
+        <v>0.1249574895259502</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>0.1668733205659571</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2052.691483934354</v>
+        <v>1589.944090635409</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>6053871.211811053</v>
-      </c>
-      <c r="G38" s="39" t="n">
-        <v>26000229.81497657</v>
+        <v>6026382.544975105</v>
+      </c>
+      <c r="G38" s="38" t="n">
+        <v>34124729.14612774</v>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="37" t="inlineStr">
+      <c r="B39" s="36" t="inlineStr">
         <is>
           <t>95% / 70%</t>
         </is>
       </c>
       <c r="C39" s="13" t="n">
-        <v>0.2448789571694599</v>
-      </c>
-      <c r="D39" s="15" t="n">
-        <v>0.4288973384030423</v>
+        <v>0.1962089931255445</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>0.5380875348760752</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>2698.564737865702</v>
+        <v>2066.849370832875</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>7576110.32057563</v>
-      </c>
-      <c r="G39" s="39" t="n">
-        <v>33567641.51052701</v>
+        <v>7807798.343177713</v>
+      </c>
+      <c r="G39" s="38" t="n">
+        <v>45422589.64466301</v>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="37" t="inlineStr">
+      <c r="B40" s="36" t="inlineStr">
         <is>
           <t>90% / 90%</t>
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>0.3339350180505414</v>
-      </c>
-      <c r="D40" s="15" t="n">
-        <v>0.6356756756756757</v>
+        <v>0.273082837814269</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>0.7817907848321594</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>3279.651029395763</v>
+        <v>2484.551383848262</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>8781570.713777572</v>
-      </c>
-      <c r="G40" s="39" t="n">
-        <v>39560271.06886403</v>
+        <v>9343628.295485487</v>
+      </c>
+      <c r="G40" s="38" t="n">
+        <v>55162927.95767928</v>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="37" t="inlineStr">
+      <c r="B41" s="36" t="inlineStr">
         <is>
           <t>85% / 95%</t>
         </is>
       </c>
       <c r="C41" s="13" t="n">
-        <v>0.3832737030411447</v>
-      </c>
-      <c r="D41" s="15" t="n">
-        <v>0.8317386231038513</v>
+        <v>0.3221404484835234</v>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>0.9955963615821395</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>3344.29459757605</v>
+        <v>2541.471627648346</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>8411321.285592195</v>
-      </c>
-      <c r="G41" s="39" t="n">
-        <v>37719673.33557179</v>
+        <v>9483928.924521115</v>
+      </c>
+      <c r="G41" s="38" t="n">
+        <v>56052724.11661119</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  E.  SLC dilution  -  drives the back-solved heterogeneity contrast</t>
+          <t xml:space="preserve">  E.  Waste dilution  -  drives the back-solved heterogeneity contrast</t>
         </is>
       </c>
       <c r="C44" s="4" t="n"/>
@@ -10296,113 +10571,113 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="37" t="inlineStr">
+      <c r="B46" s="36" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="C46" s="15" t="n">
-        <v>2.45454545454547</v>
+      <c r="C46" s="14" t="n">
+        <v>2.418238547723792</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>0.1864406779661024</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>0.5650349650349624</v>
+        <v>0.2583489329351673</v>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>0.8278868683203929</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>5146371.279828811</v>
-      </c>
-      <c r="G46" s="39" t="n">
-        <v>21488832.38769123</v>
+        <v>8529879.698814673</v>
+      </c>
+      <c r="G46" s="38" t="n">
+        <v>50002078.85364542</v>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="37" t="inlineStr">
+      <c r="B47" s="36" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="n">
+        <v>2.22987665567021</v>
+      </c>
+      <c r="D47" s="13" t="n">
+        <v>0.2730376631833965</v>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>0.7819234545989562</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>9341142.478789536</v>
+      </c>
+      <c r="G47" s="38" t="n">
+        <v>55147162.7386416</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="36" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="C47" s="15" t="n">
-        <v>2.032258064516129</v>
-      </c>
-      <c r="D47" s="13" t="n">
-        <v>0.2164003937305975</v>
-      </c>
-      <c r="E47" s="15" t="n">
-        <v>0.4853743876836952</v>
-      </c>
-      <c r="F47" s="11" t="n">
-        <v>6394747.572014087</v>
-      </c>
-      <c r="G47" s="39" t="n">
-        <v>27694807.05982913</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="37" t="inlineStr">
+      <c r="C48" s="14" t="n">
+        <v>2.010832757720235</v>
+      </c>
+      <c r="D48" s="13" t="n">
+        <v>0.2958985534320903</v>
+      </c>
+      <c r="E48" s="14" t="n">
+        <v>0.7205586941410823</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>10593314.64231939</v>
+      </c>
+      <c r="G48" s="38" t="n">
+        <v>63088524.00757338</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="36" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="C48" s="15" t="n">
-        <v>1.799999999999999</v>
-      </c>
-      <c r="D48" s="13" t="n">
-        <v>0.2448789571694599</v>
-      </c>
-      <c r="E48" s="15" t="n">
-        <v>0.4288973384030423</v>
-      </c>
-      <c r="F48" s="11" t="n">
-        <v>7576110.32057563</v>
-      </c>
-      <c r="G48" s="39" t="n">
-        <v>33567641.51052701</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="37" t="inlineStr">
+      <c r="C49" s="14" t="n">
+        <v>1.785258088158306</v>
+      </c>
+      <c r="D49" s="13" t="n">
+        <v>0.3313059649696605</v>
+      </c>
+      <c r="E49" s="14" t="n">
+        <v>0.6436958150026263</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>12516607.98390734</v>
+      </c>
+      <c r="G49" s="38" t="n">
+        <v>75286181.56340417</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="36" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="C49" s="15" t="n">
-        <v>1.653061224489796</v>
-      </c>
-      <c r="D49" s="13" t="n">
-        <v>0.2728176011355571</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <v>0.385431841831426</v>
-      </c>
-      <c r="F49" s="11" t="n">
-        <v>8733005.700064503</v>
-      </c>
-      <c r="G49" s="39" t="n">
-        <v>39318842.86573166</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="37" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="C50" s="15" t="n">
-        <v>1.551724137931034</v>
+      <c r="C50" s="14" t="n">
+        <v>1.641992745481975</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>0.3005586592178771</v>
-      </c>
-      <c r="E50" s="15" t="n">
-        <v>0.3505045140732876</v>
+        <v>0.3659233802915431</v>
+      </c>
+      <c r="E50" s="14" t="n">
+        <v>0.5838125120979593</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>9881143.212659189</v>
-      </c>
-      <c r="G50" s="39" t="n">
-        <v>45026506.78717735</v>
+        <v>14386773.32155108</v>
+      </c>
+      <c r="G50" s="38" t="n">
+        <v>87146897.69447999</v>
       </c>
     </row>
     <row r="53">
@@ -10444,92 +10719,92 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="37" t="n">
+      <c r="B55" s="36" t="n">
         <v>2500</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>3528263.213777077</v>
-      </c>
-      <c r="D55" s="41" t="n">
-        <v>15109546.99691464</v>
-      </c>
-      <c r="E55" s="41" t="n">
-        <v>13444833.36467169</v>
-      </c>
-      <c r="F55" s="41" t="n">
-        <v>10020168.80743885</v>
+        <v>5616801.219713095</v>
+      </c>
+      <c r="D55" s="40" t="n">
+        <v>31527136.44470212</v>
+      </c>
+      <c r="E55" s="40" t="n">
+        <v>27966861.07193018</v>
+      </c>
+      <c r="F55" s="40" t="n">
+        <v>20899183.14443435</v>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="37" t="n">
+      <c r="B56" s="36" t="n">
         <v>3000</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>4877545.582709928</v>
-      </c>
-      <c r="D56" s="41" t="n">
-        <v>22453771.36348042</v>
-      </c>
-      <c r="E56" s="41" t="n">
-        <v>20152436.07995679</v>
-      </c>
-      <c r="F56" s="41" t="n">
-        <v>15418107.46802981</v>
+        <v>6859076.911637226</v>
+      </c>
+      <c r="D56" s="40" t="n">
+        <v>39405733.61569451</v>
+      </c>
+      <c r="E56" s="40" t="n">
+        <v>35058027.21605482</v>
+      </c>
+      <c r="F56" s="40" t="n">
+        <v>26427181.18909661</v>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="37" t="n">
+      <c r="B57" s="36" t="n">
         <v>3500</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>6226827.951642781</v>
-      </c>
-      <c r="D57" s="41" t="n">
-        <v>29797995.7300462</v>
-      </c>
-      <c r="E57" s="41" t="n">
-        <v>26860038.79524191</v>
-      </c>
-      <c r="F57" s="41" t="n">
-        <v>20816046.12862078</v>
+        <v>8101352.603561359</v>
+      </c>
+      <c r="D57" s="40" t="n">
+        <v>47284330.78668692</v>
+      </c>
+      <c r="E57" s="40" t="n">
+        <v>42149193.36017944</v>
+      </c>
+      <c r="F57" s="40" t="n">
+        <v>31955179.2337589</v>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="37" t="n">
+      <c r="B58" s="36" t="n">
         <v>4000</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>7576110.32057563</v>
-      </c>
-      <c r="D58" s="41" t="n">
-        <v>37142220.09661198</v>
-      </c>
-      <c r="E58" s="41" t="n">
-        <v>33567641.51052701</v>
-      </c>
-      <c r="F58" s="41" t="n">
-        <v>26213984.78921172</v>
+        <v>9343628.295485487</v>
+      </c>
+      <c r="D58" s="40" t="n">
+        <v>55162927.95767928</v>
+      </c>
+      <c r="E58" s="40" t="n">
+        <v>49240359.50430406</v>
+      </c>
+      <c r="F58" s="40" t="n">
+        <v>37483177.27842114</v>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="37" t="n">
+      <c r="B59" s="36" t="n">
         <v>4500</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>8925392.689508483</v>
-      </c>
-      <c r="D59" s="41" t="n">
-        <v>44486444.46317773</v>
-      </c>
-      <c r="E59" s="41" t="n">
-        <v>40275244.22581213</v>
-      </c>
-      <c r="F59" s="41" t="n">
-        <v>31611923.44980269</v>
+        <v>10585903.98740962</v>
+      </c>
+      <c r="D59" s="40" t="n">
+        <v>63041525.12867167</v>
+      </c>
+      <c r="E59" s="40" t="n">
+        <v>56331525.64842871</v>
+      </c>
+      <c r="F59" s="40" t="n">
+        <v>43011175.32308343</v>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="42" t="inlineStr">
+      <c r="B62" s="41" t="inlineStr">
         <is>
           <t>NPV breakeven on capacity capture is ~29%; cash breakeven ~21%.</t>
         </is>
